--- a/outputs/q4/validation/q4_validation.xlsx
+++ b/outputs/q4/validation/q4_validation.xlsx
@@ -484,7 +484,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8884</v>
+        <v>8202</v>
       </c>
     </row>
     <row r="6">
@@ -495,7 +495,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1d38144c0bc5b591da1abf7762067948afc4e832bf85bde93da9e1af4ffe8e7e</t>
+          <t>ec30af5a87d527d514081a35e7564bb41f74248331f3a2bc1d52472c540b3d3b</t>
         </is>
       </c>
     </row>
